--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:46:49+00:00</t>
+    <t>2026-03-23T16:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -725,7 +725,7 @@
     <t>Patient.identifier:nationalid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_nationalId</t>
+    <t>http://openelis-global.org/pat_nationalId</t>
   </si>
   <si>
     <t>Patient.identifier:nationalid.value</t>
@@ -758,7 +758,7 @@
     <t>Patient.identifier:subjectnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_subjectNumber</t>
+    <t>http://openelis-global.org/pat_subjectNumber</t>
   </si>
   <si>
     <t>Patient.identifier:subjectnumber.value</t>
@@ -791,7 +791,7 @@
     <t>Patient.identifier:stnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_stNumber</t>
+    <t>http://openelis-global.org/pat_stNumber</t>
   </si>
   <si>
     <t>Patient.identifier:stnumber.value</t>
@@ -824,7 +824,7 @@
     <t>Patient.identifier:guid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_guid</t>
+    <t>http://openelis-global.org/pat_guid</t>
   </si>
   <si>
     <t>Patient.identifier:guid.value</t>
@@ -857,7 +857,7 @@
     <t>Patient.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_uuid</t>
+    <t>http://openelis-global.org/pat_uuid</t>
   </si>
   <si>
     <t>Patient.identifier:uuid.value</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:01:57+00:00</t>
+    <t>2026-05-11T11:00:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:00:24+00:00</t>
+    <t>2026-05-11T11:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
